--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 11:16</t>
+          <t>更新时间: 2026-09-16 11:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 11:22</t>
+          <t>更新时间: 2026-09-16 12:18</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 12:18</t>
+          <t>更新时间: 2026-09-17 07:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 07:49</t>
+          <t>更新时间: 2026-09-17 08:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 08:35</t>
+          <t>更新时间: 2026-09-17 09:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 09:10</t>
+          <t>更新时间: 2026-09-17 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 10:32</t>
+          <t>更新时间: 2026-09-17 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 12:06</t>
+          <t>更新时间: 2026-09-18 07:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 07:44</t>
+          <t>更新时间: 2026-09-18 08:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 08:34</t>
+          <t>更新时间: 2026-09-18 09:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 09:10</t>
+          <t>更新时间: 2026-09-18 10:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 10:33</t>
+          <t>更新时间: 2026-09-18 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 12:06</t>
+          <t>更新时间: 2026-09-19 07:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 07:45</t>
+          <t>更新时间: 2026-09-19 08:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 08:34</t>
+          <t>更新时间: 2026-09-19 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:09</t>
+          <t>更新时间: 2026-09-19 10:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 10:31</t>
+          <t>更新时间: 2026-09-19 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 12:06</t>
+          <t>更新时间: 2026-09-20 07:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 07:45</t>
+          <t>更新时间: 2026-09-20 08:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 08:36</t>
+          <t>更新时间: 2026-09-20 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 09:09</t>
+          <t>更新时间: 2026-09-20 10:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 10:31</t>
+          <t>更新时间: 2026-09-20 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 12:06</t>
+          <t>更新时间: 2026-09-21 07:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 07:45</t>
+          <t>更新时间: 2026-09-21 08:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 08:36</t>
+          <t>更新时间: 2026-09-21 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:09</t>
+          <t>更新时间: 2026-09-21 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 10:32</t>
+          <t>更新时间: 2026-09-21 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 12:06</t>
+          <t>更新时间: 2026-09-22 07:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 07:48</t>
+          <t>更新时间: 2026-09-22 08:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 08:35</t>
+          <t>更新时间: 2026-09-22 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 09:09</t>
+          <t>更新时间: 2026-09-22 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 10:32</t>
+          <t>更新时间: 2026-09-22 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 12:06</t>
+          <t>更新时间: 2026-09-23 07:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 07:47</t>
+          <t>更新时间: 2026-09-23 08:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 08:33</t>
+          <t>更新时间: 2026-09-23 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:09</t>
+          <t>更新时间: 2026-09-23 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 10:32</t>
+          <t>更新时间: 2026-09-23 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 12:06</t>
+          <t>更新时间: 2026-09-24 07:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 07:49</t>
+          <t>更新时间: 2026-09-24 08:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 08:36</t>
+          <t>更新时间: 2026-09-24 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 09:09</t>
+          <t>更新时间: 2026-09-24 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 10:32</t>
+          <t>更新时间: 2026-09-24 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 12:06</t>
+          <t>更新时间: 2026-09-25 07:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 07:47</t>
+          <t>更新时间: 2026-09-25 08:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 08:36</t>
+          <t>更新时间: 2026-09-25 09:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 09:10</t>
+          <t>更新时间: 2026-09-25 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 10:32</t>
+          <t>更新时间: 2026-09-25 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 12:06</t>
+          <t>更新时间: 2026-09-26 07:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 07:47</t>
+          <t>更新时间: 2026-09-26 08:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 08:35</t>
+          <t>更新时间: 2026-09-26 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 09:09</t>
+          <t>更新时间: 2026-09-26 10:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 10:31</t>
+          <t>更新时间: 2026-09-26 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 12:06</t>
+          <t>更新时间: 2026-09-27 07:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 07:47</t>
+          <t>更新时间: 2026-09-27 08:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 08:37</t>
+          <t>更新时间: 2026-09-27 09:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:09</t>
+          <t>更新时间: 2026-09-27 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 10:32</t>
+          <t>更新时间: 2026-09-27 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 12:06</t>
+          <t>更新时间: 2026-09-28 07:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 07:48</t>
+          <t>更新时间: 2026-09-28 08:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 08:38</t>
+          <t>更新时间: 2026-09-28 09:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 09:10</t>
+          <t>更新时间: 2026-09-28 10:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 10:33</t>
+          <t>更新时间: 2026-09-28 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 12:07</t>
+          <t>更新时间: 2026-09-29 07:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 07:49</t>
+          <t>更新时间: 2026-09-29 08:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 08:37</t>
+          <t>更新时间: 2026-09-29 09:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 09:11</t>
+          <t>更新时间: 2026-09-29 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 10:32</t>
+          <t>更新时间: 2026-09-29 12:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 12:06</t>
+          <t>更新时间: 2026-09-30 07:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 07:52</t>
+          <t>更新时间: 2026-09-30 08:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 08:39</t>
+          <t>更新时间: 2026-09-30 09:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 09:11</t>
+          <t>更新时间: 2026-09-30 10:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 10:33</t>
+          <t>更新时间: 2026-09-30 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 12:07</t>
+          <t>更新时间: 2026-10-01 07:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 07:51</t>
+          <t>更新时间: 2026-10-01 08:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 08:41</t>
+          <t>更新时间: 2026-10-01 09:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 09:12</t>
+          <t>更新时间: 2026-10-01 10:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 10:34</t>
+          <t>更新时间: 2026-10-01 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 12:07</t>
+          <t>更新时间: 2026-10-02 07:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 07:50</t>
+          <t>更新时间: 2026-10-02 08:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 08:39</t>
+          <t>更新时间: 2026-10-02 09:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 09:11</t>
+          <t>更新时间: 2026-10-02 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 10:32</t>
+          <t>更新时间: 2026-10-02 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 12:07</t>
+          <t>更新时间: 2026-10-03 07:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 07:53</t>
+          <t>更新时间: 2026-10-03 08:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 08:37</t>
+          <t>更新时间: 2026-10-03 09:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 09:10</t>
+          <t>更新时间: 2026-10-03 10:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:43</t>
+          <t>更新时间: 2026-10-03 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 12:10</t>
+          <t>更新时间: 2026-10-04 11:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 11:16</t>
+          <t>更新时间: 2026-10-04 11:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 11:51</t>
+          <t>更新时间: 2026-10-04 12:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 12:00</t>
+          <t>更新时间: 2026-10-04 12:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 12:11</t>
+          <t>更新时间: 2026-10-04 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 13:36</t>
+          <t>更新时间: 2026-10-05 07:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 07:50</t>
+          <t>更新时间: 2026-10-05 08:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 08:42</t>
+          <t>更新时间: 2026-10-05 09:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 09:12</t>
+          <t>更新时间: 2026-10-05 10:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 10:36</t>
+          <t>更新时间: 2026-10-05 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 12:10</t>
+          <t>更新时间: 2026-10-06 07:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 07:50</t>
+          <t>更新时间: 2026-10-06 08:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 08:43</t>
+          <t>更新时间: 2026-10-06 09:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 09:11</t>
+          <t>更新时间: 2026-10-06 10:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 10:35</t>
+          <t>更新时间: 2026-10-06 12:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 12:08</t>
+          <t>更新时间: 2026-10-07 07:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 07:50</t>
+          <t>更新时间: 2026-10-07 08:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 08:44</t>
+          <t>更新时间: 2026-10-07 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 09:13</t>
+          <t>更新时间: 2026-10-07 10:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 10:36</t>
+          <t>更新时间: 2026-10-07 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 12:07</t>
+          <t>更新时间: 2026-10-08 07:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 07:54</t>
+          <t>更新时间: 2026-10-08 08:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 08:43</t>
+          <t>更新时间: 2026-10-08 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 09:13</t>
+          <t>更新时间: 2026-10-08 10:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 10:34</t>
+          <t>更新时间: 2026-10-08 12:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 12:08</t>
+          <t>更新时间: 2026-10-09 07:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 07:54</t>
+          <t>更新时间: 2026-10-09 08:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 08:45</t>
+          <t>更新时间: 2026-10-09 09:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 09:15</t>
+          <t>更新时间: 2026-10-09 10:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 10:35</t>
+          <t>更新时间: 2026-10-09 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 12:07</t>
+          <t>更新时间: 2026-10-10 07:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 07:55</t>
+          <t>更新时间: 2026-10-10 08:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 08:44</t>
+          <t>更新时间: 2026-10-10 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 09:13</t>
+          <t>更新时间: 2026-10-10 10:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 10:36</t>
+          <t>更新时间: 2026-10-10 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 12:07</t>
+          <t>更新时间: 2026-10-11 07:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 07:49</t>
+          <t>更新时间: 2026-10-11 08:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 08:43</t>
+          <t>更新时间: 2026-10-11 09:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 09:12</t>
+          <t>更新时间: 2026-10-11 10:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 10:36</t>
+          <t>更新时间: 2026-10-11 12:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 12:07</t>
+          <t>更新时间: 2026-10-12 07:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 07:51</t>
+          <t>更新时间: 2026-10-12 08:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 08:46</t>
+          <t>更新时间: 2026-10-12 09:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 09:16</t>
+          <t>更新时间: 2026-10-12 10:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 10:39</t>
+          <t>更新时间: 2026-10-12 12:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 12:09</t>
+          <t>更新时间: 2026-10-13 07:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 07:53</t>
+          <t>更新时间: 2026-10-13 08:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 08:47</t>
+          <t>更新时间: 2026-10-13 09:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 09:16</t>
+          <t>更新时间: 2026-10-13 10:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 10:39</t>
+          <t>更新时间: 2026-10-13 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 12:10</t>
+          <t>更新时间: 2026-10-14 08:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 08:01</t>
+          <t>更新时间: 2026-10-14 08:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 08:58</t>
+          <t>更新时间: 2026-10-14 09:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 09:27</t>
+          <t>更新时间: 2026-10-14 10:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 10:50</t>
+          <t>更新时间: 2026-10-14 12:20</t>
         </is>
       </c>
     </row>
